--- a/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CE42C52-7993-468E-904F-E638B77BD3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C86D60C-CACB-4D96-8221-78B708265C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -40,6 +40,32 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{2FF9EF2B-EBD7-4C7E-9F26-8FF1228838F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+11-09-2025
+AFS will be sufficient
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D8" authorId="0" shapeId="0" xr:uid="{79577DE7-359E-49C1-A1D9-EC64BAD436CB}">
       <text>
         <r>
@@ -97,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="92">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -294,9 +320,6 @@
     <t>UCE_max nuclear capacity</t>
   </si>
   <si>
-    <t>UC_RHSRT~2050</t>
-  </si>
-  <si>
     <t>life</t>
   </si>
   <si>
@@ -357,6 +380,15 @@
     <t>wind*</t>
   </si>
   <si>
+    <t>~UC_T: 2050</t>
+  </si>
+  <si>
+    <t>base-year nuclear capacity</t>
+  </si>
+  <si>
+    <t>\I: hydro</t>
+  </si>
+  <si>
     <t>windon</t>
   </si>
   <si>
@@ -376,7 +408,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,8 +458,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,6 +492,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -474,13 +527,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -491,10 +545,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Heading 4" xfId="3" builtinId="19"/>
+    <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -867,7 +924,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="AD1">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.45">
@@ -941,15 +998,12 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4">
-        <f>IFERROR(VLOOKUP(B5,$F$3:$J$11,5,FALSE),"")</f>
-        <v>0.37031923094731656</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="F5" t="s">
         <v>8</v>
       </c>
@@ -971,7 +1025,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -1004,7 +1058,7 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -1146,7 +1200,7 @@
       </c>
       <c r="AJ8">
         <f>AI8*$AD$1</f>
-        <v>0.52035444288011523</v>
+        <v>0.11563432064002561</v>
       </c>
       <c r="AK8">
         <v>0</v>
@@ -1214,7 +1268,7 @@
       </c>
       <c r="AJ9">
         <f>AI9*$AD$1</f>
-        <v>0.14821050483406037</v>
+        <v>3.2935667740902307E-2</v>
       </c>
       <c r="AK9">
         <v>0</v>
@@ -1225,7 +1279,7 @@
     </row>
     <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3">
         <v>0.12065189145042136</v>
@@ -1251,7 +1305,7 @@
         <v>26</v>
       </c>
       <c r="U13" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.45">
@@ -1291,9 +1345,6 @@
       <c r="AC14" t="s">
         <v>17</v>
       </c>
-      <c r="AD14" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
@@ -1307,7 +1358,7 @@
         <v>Hydropower - large-scale unit,Solar photovoltaics - Large scale unit,Wind offshore,Wind onshore</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U15" t="s">
         <v>64</v>
@@ -1319,15 +1370,18 @@
         <v>1</v>
       </c>
       <c r="AB15">
+        <f>AE15*2.5</f>
+        <v>16.95</v>
+      </c>
+      <c r="AC15">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="11">
         <f>SUMIFS(historical_data_long!$D$3:$D$626,historical_data_long!$A$3:$A$626,Veda!$V15,historical_data_long!$C$3:$C$626,"GW",historical_data_long!$B$3:$B$626,2022)</f>
         <v>6.78</v>
       </c>
-      <c r="AC15">
-        <v>3</v>
-      </c>
-      <c r="AD15">
-        <f>AB15*2.5</f>
-        <v>16.95</v>
+      <c r="AF15" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.45">
@@ -1469,24 +1523,24 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28">
         <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29">
         <v>8.76</v>
       </c>
       <c r="G29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.45">
@@ -1549,7 +1603,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.45">
       <c r="D40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E40">
         <v>-1</v>
@@ -1557,7 +1611,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1580,41 +1635,41 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>71</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>72</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>73</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>74</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>75</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>76</v>
-      </c>
-      <c r="J10" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C11">
         <v>20</v>
@@ -1648,7 +1703,7 @@
     </row>
     <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -1656,16 +1711,16 @@
         <v>48</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="F19" s="8">
         <v>2025</v>
@@ -1690,7 +1745,7 @@
         <v>solar</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1720,7 +1775,7 @@
         <v>wind*</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1750,7 +1805,7 @@
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1780,7 +1835,7 @@
         <v>nuclear</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1921,7 +1976,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B9">
         <v>2000</v>
@@ -2033,7 +2088,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B17">
         <v>2001</v>
@@ -2145,7 +2200,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B25">
         <v>2002</v>
@@ -2257,7 +2312,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B33">
         <v>2003</v>
@@ -2369,7 +2424,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B41">
         <v>2004</v>
@@ -2481,7 +2536,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B49">
         <v>2005</v>
@@ -2593,7 +2648,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B57">
         <v>2006</v>
@@ -2705,7 +2760,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B65">
         <v>2007</v>
@@ -2817,7 +2872,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B73">
         <v>2008</v>
@@ -2929,7 +2984,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B81">
         <v>2009</v>
@@ -3041,7 +3096,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B89">
         <v>2010</v>
@@ -3153,7 +3208,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B97">
         <v>2011</v>
@@ -3265,7 +3320,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B105">
         <v>2012</v>
@@ -3377,7 +3432,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B113">
         <v>2013</v>
@@ -3489,7 +3544,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B121">
         <v>2014</v>
@@ -3601,7 +3656,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B129">
         <v>2015</v>
@@ -3713,7 +3768,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B137">
         <v>2016</v>
@@ -3825,7 +3880,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B145">
         <v>2017</v>
@@ -3937,7 +3992,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B153">
         <v>2018</v>
@@ -4049,7 +4104,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B161">
         <v>2019</v>
@@ -4161,7 +4216,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B169">
         <v>2020</v>
@@ -4273,7 +4328,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B177">
         <v>2021</v>
@@ -4385,7 +4440,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B185">
         <v>2022</v>
@@ -4497,7 +4552,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B193">
         <v>2023</v>
@@ -4609,7 +4664,7 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B201">
         <v>2000</v>
@@ -4721,7 +4776,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B209">
         <v>2001</v>
@@ -4833,7 +4888,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B217">
         <v>2002</v>
@@ -4945,7 +5000,7 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B225">
         <v>2003</v>
@@ -5057,7 +5112,7 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B233">
         <v>2004</v>
@@ -5169,7 +5224,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B241">
         <v>2005</v>
@@ -5281,7 +5336,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B249">
         <v>2006</v>
@@ -5393,7 +5448,7 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B257">
         <v>2007</v>
@@ -5505,7 +5560,7 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B265">
         <v>2008</v>
@@ -5617,7 +5672,7 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B273">
         <v>2009</v>
@@ -5729,7 +5784,7 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B281">
         <v>2010</v>
@@ -5841,7 +5896,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B289">
         <v>2011</v>
@@ -5953,7 +6008,7 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B297">
         <v>2012</v>
@@ -6065,7 +6120,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B305">
         <v>2013</v>
@@ -6177,7 +6232,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B313">
         <v>2014</v>
@@ -6289,7 +6344,7 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B321">
         <v>2015</v>
@@ -6401,7 +6456,7 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B329">
         <v>2016</v>
@@ -6513,7 +6568,7 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B337">
         <v>2017</v>
@@ -6625,7 +6680,7 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B345">
         <v>2018</v>
@@ -6737,7 +6792,7 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B353">
         <v>2019</v>
@@ -6849,7 +6904,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B361">
         <v>2020</v>
@@ -6961,7 +7016,7 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B369">
         <v>2021</v>
@@ -7073,7 +7128,7 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B377">
         <v>2022</v>
@@ -7185,7 +7240,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B385">
         <v>2023</v>
@@ -7297,7 +7352,7 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B393">
         <v>2000</v>
@@ -7409,7 +7464,7 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B401">
         <v>2001</v>
@@ -7521,7 +7576,7 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B409">
         <v>2002</v>
@@ -7633,7 +7688,7 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B417">
         <v>2003</v>
@@ -7745,7 +7800,7 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B425">
         <v>2004</v>
@@ -7857,7 +7912,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B433">
         <v>2005</v>
@@ -7969,7 +8024,7 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B441">
         <v>2006</v>
@@ -8081,7 +8136,7 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B449">
         <v>2007</v>
@@ -8193,7 +8248,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B457">
         <v>2008</v>
@@ -8305,7 +8360,7 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B465">
         <v>2009</v>
@@ -8417,7 +8472,7 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B473">
         <v>2010</v>
@@ -8529,7 +8584,7 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B481">
         <v>2011</v>
@@ -8641,7 +8696,7 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B489">
         <v>2012</v>
@@ -8753,7 +8808,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B497">
         <v>2013</v>
@@ -8865,7 +8920,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B505">
         <v>2014</v>
@@ -8977,7 +9032,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B513">
         <v>2015</v>
@@ -9089,7 +9144,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B521">
         <v>2016</v>
@@ -9201,7 +9256,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B529">
         <v>2017</v>
@@ -9313,7 +9368,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B537">
         <v>2018</v>
@@ -9425,7 +9480,7 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B545">
         <v>2019</v>
@@ -9537,7 +9592,7 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B553">
         <v>2020</v>
@@ -9649,7 +9704,7 @@
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B561">
         <v>2021</v>
@@ -9761,7 +9816,7 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B569">
         <v>2022</v>
@@ -9873,7 +9928,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B577">
         <v>2023</v>

--- a/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C86D60C-CACB-4D96-8221-78B708265C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBD4C032-CF31-496F-B40A-2A84792D8B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBD4C032-CF31-496F-B40A-2A84792D8B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3877D4E2-13B3-451A-9E78-81A26FFC8566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3877D4E2-13B3-451A-9E78-81A26FFC8566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E22F5F88-F1DC-4C72-A2BE-C4ED76AD388D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E22F5F88-F1DC-4C72-A2BE-C4ED76AD388D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98825FEF-8AB8-4286-AECA-6C0E1DC72D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98825FEF-8AB8-4286-AECA-6C0E1DC72D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F419D35-E580-4551-A2C5-34848DA6C34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F419D35-E580-4551-A2C5-34848DA6C34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07A266A1-E26D-4D23-B694-171FAC2C716E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07A266A1-E26D-4D23-B694-171FAC2C716E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A343B71-1D1C-47B7-A581-64FA44C13E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7ED84B3-4FF5-46D8-849A-DA49E411F399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEBB60C-2492-41D0-AF86-200C5D82E094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="re_targets" sheetId="5" r:id="rId1"/>
@@ -626,7 +626,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -642,6 +642,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2167,29 +2170,29 @@
       <c r="B11" t="s">
         <v>121</v>
       </c>
-      <c r="C11">
-        <v>20</v>
-      </c>
-      <c r="D11">
-        <v>35</v>
-      </c>
-      <c r="E11">
-        <v>8</v>
-      </c>
-      <c r="F11">
-        <v>15</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11">
-        <v>4</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <v>4</v>
+      <c r="C11" s="14">
+        <v>80</v>
+      </c>
+      <c r="D11" s="14">
+        <v>150</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>60</v>
+      </c>
+      <c r="G11" s="14">
+        <v>3</v>
+      </c>
+      <c r="H11" s="14">
+        <v>6</v>
+      </c>
+      <c r="I11" s="14">
+        <v>3</v>
+      </c>
+      <c r="J11" s="14">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.45">
@@ -2248,11 +2251,11 @@
       </c>
       <c r="F20">
         <f>C11</f>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <f>D11</f>
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -2278,11 +2281,11 @@
       </c>
       <c r="F21">
         <f>E11</f>
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G21">
         <f>F11</f>
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -2308,11 +2311,11 @@
       </c>
       <c r="F22">
         <f>G11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
         <f>H11</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -2338,11 +2341,11 @@
       </c>
       <c r="F23">
         <f>I11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <f>J11</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H23">
         <v>4</v>
